--- a/i_test/05_05_test_adding_PROMPT/i_input_xlsx/Person_rel_PROMPT_dataset.xlsx
+++ b/i_test/05_05_test_adding_PROMPT/i_input_xlsx/Person_rel_PROMPT_dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giorg\GitHub\ConcePTIONAlgorithmPregnancies\i_test\05_05_test_adding_PROMPT\i_input_xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01352180-8CF6-4EE4-82D2-B4E1D5AD72AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51E2299-1EF8-4743-804C-3146AB188A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="26610" windowHeight="14130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15495" yWindow="0" windowWidth="13410" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="24">
   <si>
     <t>child_id</t>
   </si>
@@ -77,6 +77,21 @@
   </si>
   <si>
     <t>child_1_person_1</t>
+  </si>
+  <si>
+    <t>person_3_UNK</t>
+  </si>
+  <si>
+    <t>child_1_person_3_UNK</t>
+  </si>
+  <si>
+    <t>child_1_person_4_UNK</t>
+  </si>
+  <si>
+    <t>person_4_UNK</t>
+  </si>
+  <si>
+    <t>child_2_person_3_UNK</t>
   </si>
 </sst>
 </file>
@@ -92,12 +107,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -112,8 +139,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -410,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.85546875" customWidth="1"/>
@@ -577,6 +606,84 @@
         <v>1</v>
       </c>
     </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="1">
+        <v>20101215</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="1">
+        <v>20201215</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="2">
+        <v>20201215</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/i_test/05_05_test_adding_PROMPT/i_input_xlsx/Person_rel_PROMPT_dataset.xlsx
+++ b/i_test/05_05_test_adding_PROMPT/i_input_xlsx/Person_rel_PROMPT_dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giorg\GitHub\ConcePTIONAlgorithmPregnancies\i_test\05_05_test_adding_PROMPT\i_input_xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51E2299-1EF8-4743-804C-3146AB188A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D022124-35B2-4504-BE2C-529F58E94CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15495" yWindow="0" windowWidth="13410" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11052" yWindow="0" windowWidth="12084" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="28">
   <si>
     <t>child_id</t>
   </si>
@@ -92,6 +92,18 @@
   </si>
   <si>
     <t>child_2_person_3_UNK</t>
+  </si>
+  <si>
+    <t>child_1_person_1_rule3</t>
+  </si>
+  <si>
+    <t>child_1_person_2_rule3</t>
+  </si>
+  <si>
+    <t>person_1_rule3</t>
+  </si>
+  <si>
+    <t>person_2_rule3</t>
   </si>
 </sst>
 </file>
@@ -107,7 +119,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -126,6 +138,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -139,10 +157,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -439,18 +458,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.85546875" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -476,7 +495,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -502,7 +521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -528,7 +547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -554,7 +573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -580,7 +599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -606,7 +625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -632,7 +651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -658,7 +677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -681,6 +700,58 @@
         <v>1</v>
       </c>
       <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="3">
+        <v>20201215</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="3">
+        <v>20201215</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3">
         <v>1</v>
       </c>
     </row>

--- a/i_test/05_05_test_adding_PROMPT/i_input_xlsx/Person_rel_PROMPT_dataset.xlsx
+++ b/i_test/05_05_test_adding_PROMPT/i_input_xlsx/Person_rel_PROMPT_dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giorg\GitHub\ConcePTIONAlgorithmPregnancies\i_test\05_05_test_adding_PROMPT\i_input_xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D022124-35B2-4504-BE2C-529F58E94CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C39ADD5-EC14-473D-8954-45ABB1262FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11052" yWindow="0" windowWidth="12084" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="32">
   <si>
     <t>child_id</t>
   </si>
@@ -104,6 +104,18 @@
   </si>
   <si>
     <t>person_2_rule3</t>
+  </si>
+  <si>
+    <t>person_1_rule5</t>
+  </si>
+  <si>
+    <t>child_1_person_1_rule5</t>
+  </si>
+  <si>
+    <t>child_1_person_2_rule5</t>
+  </si>
+  <si>
+    <t>person_2_rule5</t>
   </si>
 </sst>
 </file>
@@ -119,7 +131,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -144,6 +156,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -157,11 +175,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -458,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.88671875" customWidth="1"/>
@@ -755,6 +774,58 @@
         <v>1</v>
       </c>
     </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="4">
+        <v>20191215</v>
+      </c>
+      <c r="G12" s="4">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="4">
+        <v>20191215</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
